--- a/output/keep_ids.xlsx
+++ b/output/keep_ids.xlsx
@@ -12,9 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t xml:space="preserve">participant_id</t>
+    <t xml:space="preserve">responseid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R_3Pw8eqtaKwkReOR</t>
   </si>
 </sst>
 </file>
@@ -348,6 +351,11 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
